--- a/02-VALUATION/M07/bus311-valuation-m07-l01-apex-ipo-activity.xlsx
+++ b/02-VALUATION/M07/bus311-valuation-m07-l01-apex-ipo-activity.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 1 – Assumptions" sheetId="1" r:id="R53bef45bda014d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 2 – Valuation" sheetId="2" r:id="Rc3c4ab43cd664cac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 2a – Earnings" sheetId="3" r:id="R091f52d3c82e4f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 3 – Ratio Analysis" sheetId="4" r:id="R3cfc6ee827b743d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 4 – Scenario Analysis" sheetId="5" r:id="Rdfa2612cb2b64e9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="6" r:id="Rbadbe1b89c0749cd"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="Tab 1 – Assumptions" sheetId="1" ns1:id="R5f71c3034c65473b"/>
+    <ns0:sheet name="Tab 2 – Valuation" sheetId="2" ns1:id="Raf8c3b650c6e45c3"/>
+    <ns0:sheet name="Tab 2a – Earnings" sheetId="3" ns1:id="R82c9021cb8804b09"/>
+    <ns0:sheet name="Tab 3 – Ratio Analysis" sheetId="4" ns1:id="Rda43883e1226485b"/>
+    <ns0:sheet name="Tab 4 – Scenario Analysis" sheetId="5" ns1:id="R071dae525bbd400f"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18,14 +17,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="0.0%;[Red](0.0%);-"/>
     <x:numFmt numFmtId="201" formatCode="$#,##0;[Red]($#,##0);-"/>
     <x:numFmt numFmtId="202" formatCode="$0.00;[Red]($0.00);-"/>
     <x:numFmt numFmtId="203" formatCode="0.00x;[Red](0.00x);-"/>
     <x:numFmt numFmtId="204" formatCode="#,##0;[Red](#,##0);-"/>
+    <x:numFmt numFmtId="205" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -91,8 +91,31 @@
       <x:color rgb="FF1F2A5C"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF142D43"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF142D43"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFE6A817"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -124,8 +147,18 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF202A5B"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="16">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -245,11 +278,25 @@
         <x:color rgb="FFC8D2E3"/>
       </x:left>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCFD9DF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFCFD9DF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFCFD9DF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFCFD9DF"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="172">
+  <x:cellXfs count="198">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -675,6 +722,74 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="13" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="13" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -886,6 +1001,7 @@
     <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31" customHeight="1">
@@ -936,7 +1052,7 @@
         <x:v>Units</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
-        <x:v>Source / modeling note</x:v>
+        <x:v>Calculation note</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
         <x:v>Assumption</x:v>
@@ -958,9 +1074,7 @@
       <x:c r="C6" s="21" t="str">
         <x:v>Fictional case</x:v>
       </x:c>
-      <x:c r="D6" s="21" t="str">
-        <x:v>Maintained M07 assignment guide</x:v>
-      </x:c>
+      <x:c r="D6" s="21"/>
       <x:c r="F6" s="21" t="str">
         <x:v>Next-year dividend (D₁)</x:v>
       </x:c>
@@ -981,9 +1095,7 @@
       <x:c r="C7" s="21" t="str">
         <x:v>Annual</x:v>
       </x:c>
-      <x:c r="D7" s="21" t="str">
-        <x:v>Pre-IPO source period</x:v>
-      </x:c>
+      <x:c r="D7" s="21"/>
       <x:c r="F7" s="21" t="str">
         <x:v>Required return on equity</x:v>
       </x:c>
@@ -1050,9 +1162,7 @@
       <x:c r="C10" s="21" t="str">
         <x:v>%</x:v>
       </x:c>
-      <x:c r="D10" s="21" t="str">
-        <x:v>Case assumption</x:v>
-      </x:c>
+      <x:c r="D10" s="21"/>
       <x:c r="F10" s="21" t="str">
         <x:v>WACC</x:v>
       </x:c>
@@ -1073,9 +1183,7 @@
       <x:c r="C11" s="21" t="str">
         <x:v>%</x:v>
       </x:c>
-      <x:c r="D11" s="21" t="str">
-        <x:v>Case assumption</x:v>
-      </x:c>
+      <x:c r="D11" s="21"/>
       <x:c r="F11" s="21" t="str">
         <x:v>Long-run FCFF growth</x:v>
       </x:c>
@@ -1105,9 +1213,7 @@
       <x:c r="G12" s="47" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H12" s="21" t="str">
-        <x:v>Replace or defend with FactSet evidence</x:v>
-      </x:c>
+      <x:c r="H12" s="21"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21" t="str">
@@ -1128,9 +1234,7 @@
       <x:c r="G13" s="47" t="n">
         <x:v>2.2</x:v>
       </x:c>
-      <x:c r="H13" s="21" t="str">
-        <x:v>Replace or defend with FactSet evidence</x:v>
-      </x:c>
+      <x:c r="H13" s="21"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21" t="str">
@@ -1180,7 +1284,7 @@
         <x:v>400000</x:v>
       </x:c>
       <x:c r="H16" s="21" t="str">
-        <x:v>$000s from assignment guide</x:v>
+        <x:v>$000s</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1194,7 +1298,7 @@
         <x:v>Units</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
-        <x:v>Source / logic</x:v>
+        <x:v>Calculation note</x:v>
       </x:c>
       <x:c r="F17" s="21" t="str">
         <x:v>IPO issuance fees</x:v>
@@ -1216,9 +1320,7 @@
       <x:c r="C18" s="36" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D18" s="37" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D18" s="37"/>
       <x:c r="F18" s="21" t="str">
         <x:v>Net proceeds</x:v>
       </x:c>
@@ -1240,9 +1342,7 @@
       <x:c r="C19" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D19" s="40"/>
       <x:c r="F19" s="21" t="str">
         <x:v>Pre-IPO shares</x:v>
       </x:c>
@@ -1331,12 +1431,13 @@
       <x:c r="D23" s="40" t="str">
         <x:v>Debt balance times stated rates</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="str">
+      <x:c r="E23"/>
+      <x:c r="F23" s="195" t="str">
         <x:v>SCENARIO DEPLOYMENT ASSUMPTIONS</x:v>
       </x:c>
-      <x:c r="F23" s="11"/>
-      <x:c r="G23" s="11"/>
-      <x:c r="H23" s="11"/>
+      <x:c r="G23" s="193"/>
+      <x:c r="H23" s="193"/>
+      <x:c r="I23" s="194"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="38" t="str">
@@ -1352,20 +1453,21 @@
       <x:c r="D24" s="40" t="str">
         <x:v>EBIT less interest expense</x:v>
       </x:c>
-      <x:c r="E24" s="16" t="str">
+      <x:c r="E24"/>
+      <x:c r="F24" s="191" t="str">
         <x:v>Use of net proceeds</x:v>
       </x:c>
-      <x:c r="F24" s="16" t="str">
+      <x:c r="G24" s="191" t="str">
         <x:v>Scenario A</x:v>
       </x:c>
-      <x:c r="G24" s="16" t="str">
+      <x:c r="H24" s="191" t="str">
         <x:v>Scenario B</x:v>
       </x:c>
-      <x:c r="H24" s="16" t="str">
+      <x:c r="I24" s="192" t="str">
         <x:v>Scenario C</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" s="38" t="str">
         <x:v>Income tax</x:v>
       </x:c>
@@ -1379,16 +1481,17 @@
       <x:c r="D25" s="40" t="str">
         <x:v>Earnings before tax times tax rate</x:v>
       </x:c>
-      <x:c r="E25" s="21" t="str">
+      <x:c r="E25"/>
+      <x:c r="F25" s="182" t="str">
         <x:v>Scenario label</x:v>
       </x:c>
-      <x:c r="F25" s="21" t="str">
+      <x:c r="G25" s="182" t="str">
         <x:v>Maximum debt reduction</x:v>
       </x:c>
-      <x:c r="G25" s="21" t="str">
+      <x:c r="H25" s="182" t="str">
         <x:v>Growth investment</x:v>
       </x:c>
-      <x:c r="H25" s="21" t="str">
+      <x:c r="I25" s="184" t="str">
         <x:v>Balanced mix</x:v>
       </x:c>
     </x:row>
@@ -1406,30 +1509,32 @@
       <x:c r="D26" s="43" t="str">
         <x:v>Earnings before tax less income tax</x:v>
       </x:c>
-      <x:c r="E26" s="21" t="str">
+      <x:c r="E26"/>
+      <x:c r="F26" s="183" t="str">
         <x:v>Debt repayment</x:v>
       </x:c>
-      <x:c r="F26" s="23" t="n">
+      <x:c r="G26" s="196" t="n">
         <x:v>300000</x:v>
       </x:c>
-      <x:c r="G26" s="23" t="n">
+      <x:c r="H26" s="196" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="23" t="n">
+      <x:c r="I26" s="197" t="n">
         <x:v>200000</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="E27" s="21" t="str">
+      <x:c r="E27"/>
+      <x:c r="F27" s="183" t="str">
         <x:v>Growth capex / operating assets</x:v>
       </x:c>
-      <x:c r="F27" s="23" t="n">
+      <x:c r="G27" s="196" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="23" t="n">
+      <x:c r="H27" s="196" t="n">
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="H27" s="23" t="n">
+      <x:c r="I27" s="197" t="n">
         <x:v>200000</x:v>
       </x:c>
     </x:row>
@@ -1440,16 +1545,17 @@
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="11"/>
       <x:c r="D28" s="11"/>
-      <x:c r="E28" s="21" t="str">
+      <x:c r="E28"/>
+      <x:c r="F28" s="183" t="str">
         <x:v>Cash retained</x:v>
       </x:c>
-      <x:c r="F28" s="23" t="n">
+      <x:c r="G28" s="196" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="G28" s="23" t="n">
+      <x:c r="H28" s="196" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="23" t="n">
+      <x:c r="I28" s="197" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1464,21 +1570,22 @@
         <x:v>Units</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
-        <x:v>Source / logic</x:v>
-      </x:c>
-      <x:c r="E29" s="21" t="str">
+        <x:v>Calculation note</x:v>
+      </x:c>
+      <x:c r="E29"/>
+      <x:c r="F29" s="183" t="str">
         <x:v>Total uses</x:v>
       </x:c>
-      <x:c r="F29" s="23" t="n">
-        <x:f>SUM(F26:F28)</x:f>
-        <x:v>400000</x:v>
-      </x:c>
-      <x:c r="G29" s="23" t="n">
+      <x:c r="G29" s="196" t="n">
         <x:f>SUM(G26:G28)</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="H29" s="23" t="n">
+      <x:c r="H29" s="196" t="n">
         <x:f>SUM(H26:H28)</x:f>
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="I29" s="197" t="n">
+        <x:f>SUM(I26:I28)</x:f>
         <x:v>400000</x:v>
       </x:c>
     </x:row>
@@ -1492,26 +1599,25 @@
       <x:c r="C30" s="36" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D30" s="37" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
-      <x:c r="E30" s="21" t="str">
+      <x:c r="D30" s="37"/>
+      <x:c r="E30"/>
+      <x:c r="F30" s="183" t="str">
         <x:v>Sources &amp; uses check</x:v>
       </x:c>
-      <x:c r="F30" s="23" t="n">
-        <x:f>$G$18-F29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G30" s="23" t="n">
+      <x:c r="G30" s="196" t="n">
         <x:f>$G$18-G29</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="23" t="n">
+      <x:c r="H30" s="196" t="n">
         <x:f>$G$18-H29</x:f>
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="38" customHeight="1">
+      <x:c r="I30" s="197" t="n">
+        <x:f>$G$18-I29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="44" customHeight="1">
       <x:c r="A31" s="38" t="str">
         <x:v>Accounts receivable</x:v>
       </x:c>
@@ -1521,19 +1627,18 @@
       <x:c r="C31" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
-      <x:c r="E31" s="21" t="str">
+      <x:c r="D31" s="40"/>
+      <x:c r="E31"/>
+      <x:c r="F31" s="182" t="str">
         <x:v>Rationale</x:v>
       </x:c>
-      <x:c r="F31" s="21" t="str">
+      <x:c r="G31" s="182" t="str">
         <x:v>Repay all existing debt; retain excess cash</x:v>
       </x:c>
-      <x:c r="G31" s="21" t="str">
+      <x:c r="H31" s="182" t="str">
         <x:v>Fund operating assets; retain existing debt</x:v>
       </x:c>
-      <x:c r="H31" s="21" t="str">
+      <x:c r="I31" s="184" t="str">
         <x:v>Reduce leverage while funding growth</x:v>
       </x:c>
     </x:row>
@@ -1547,9 +1652,7 @@
       <x:c r="C32" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D32" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D32" s="40"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
       <x:c r="A33" s="38" t="str">
@@ -1561,12 +1664,8 @@
       <x:c r="C33" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
-      <x:c r="F33" s="62" t="str">
-        <x:v>Source note: Apex is a fictional instructional case. The maintained assignment guide states net income of $164.25 million, consistent with $219.0 million EBT less $54.75 million tax. This workbook therefore uses $164,250 ($000s), not the erroneous $164,500.</x:v>
-      </x:c>
+      <x:c r="D33" s="40"/>
+      <x:c r="F33" s="62"/>
       <x:c r="G33" s="63"/>
       <x:c r="H33" s="64"/>
     </x:row>
@@ -1580,9 +1679,7 @@
       <x:c r="C34" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D34" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D34" s="40"/>
       <x:c r="F34" s="65"/>
       <x:c r="G34" s="66"/>
       <x:c r="H34" s="67"/>
@@ -1597,9 +1694,7 @@
       <x:c r="C35" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D35" s="40"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="38" t="str">
@@ -1611,9 +1706,7 @@
       <x:c r="C36" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D36" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D36" s="40"/>
       <x:c r="F36" s="11" t="str">
         <x:v>COLOR &amp; FORMULA LEGEND</x:v>
       </x:c>
@@ -1630,9 +1723,7 @@
       <x:c r="C37" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D37" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D37" s="40"/>
       <x:c r="F37" s="71" t="str">
         <x:v>Yellow fill + blue text</x:v>
       </x:c>
@@ -1653,9 +1744,7 @@
       <x:c r="C38" s="39" t="str">
         <x:v>$000s</x:v>
       </x:c>
-      <x:c r="D38" s="40" t="str">
-        <x:v>Apex assignment guide</x:v>
-      </x:c>
+      <x:c r="D38" s="40"/>
       <x:c r="F38" s="74" t="str">
         <x:v>Gray fill + black text</x:v>
       </x:c>
@@ -1773,9 +1862,9 @@
     <x:mergeCell ref="A16:D16"/>
     <x:mergeCell ref="A28:D28"/>
     <x:mergeCell ref="F4:H4"/>
-    <x:mergeCell ref="E23:H23"/>
     <x:mergeCell ref="F33:H34"/>
     <x:mergeCell ref="F36:H36"/>
+    <x:mergeCell ref="F23:I23"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2093,7 +2182,7 @@
         <x:v>Units</x:v>
       </x:c>
       <x:c r="D19" s="16" t="str">
-        <x:v>Source / logic</x:v>
+        <x:v>Calculation note</x:v>
       </x:c>
       <x:c r="E19" s="16" t="str">
         <x:v>Student calculation</x:v>
@@ -2194,9 +2283,7 @@
       <x:c r="C23" s="39" t="str">
         <x:v>x</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="str">
-        <x:v>Replace or defend with FactSet evidence</x:v>
-      </x:c>
+      <x:c r="D23" s="40"/>
       <x:c r="E23" s="41" t="str">
         <x:v>P/S implied price</x:v>
       </x:c>
@@ -2219,21 +2306,13 @@
       <x:c r="C24" s="39" t="str">
         <x:v>x</x:v>
       </x:c>
-      <x:c r="D24" s="40" t="str">
-        <x:v>Replace or defend with FactSet evidence</x:v>
-      </x:c>
+      <x:c r="D24" s="40"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="41" t="str">
-        <x:v>FactSet evidence note</x:v>
-      </x:c>
+      <x:c r="A25" s="41"/>
       <x:c r="B25" s="86"/>
-      <x:c r="C25" s="42" t="str">
-        <x:v>Text</x:v>
-      </x:c>
-      <x:c r="D25" s="43" t="str">
-        <x:v>Record field, period, units, currency, and retrieval date on BUS311 Guide</x:v>
-      </x:c>
+      <x:c r="C25" s="42"/>
+      <x:c r="D25" s="43"/>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
       <x:c r="A27" s="11" t="str">
@@ -3947,386 +4026,4 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="31" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>EQUITY VALUATION &amp; IPO ANALYSIS — WORKFLOW</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>BUS311 · valuation-m03-l01 · student starter</x:v>
-      </x:c>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-      <x:c r="E2" s="9"/>
-      <x:c r="F2" s="9"/>
-    </x:row>
-    <x:row r="4" ht="23" customHeight="1">
-      <x:c r="A4" s="11" t="str">
-        <x:v>REQUIRED WORKFLOW</x:v>
-      </x:c>
-      <x:c r="B4" s="11"/>
-      <x:c r="C4" s="11"/>
-      <x:c r="D4" s="11"/>
-      <x:c r="E4" s="11"/>
-      <x:c r="F4" s="11"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="16" t="str">
-        <x:v>Step</x:v>
-      </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>What to do</x:v>
-      </x:c>
-      <x:c r="C5" s="16"/>
-      <x:c r="D5" s="16"/>
-      <x:c r="E5" s="16"/>
-      <x:c r="F5" s="16" t="str">
-        <x:v>Deliverable</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="138" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" s="141" t="str">
-        <x:v>Review the M07 pre-reading and the centralized assumptions tab.</x:v>
-      </x:c>
-      <x:c r="C6" s="141"/>
-      <x:c r="D6" s="141"/>
-      <x:c r="E6" s="141"/>
-      <x:c r="F6" s="142" t="str">
-        <x:v>Confirm units and case facts</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="34" customHeight="1">
-      <x:c r="A7" s="139" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B7" s="143" t="str">
-        <x:v>Document the comparison-company, market, and discount-rate evidence from FactSet.</x:v>
-      </x:c>
-      <x:c r="C7" s="143"/>
-      <x:c r="D7" s="143"/>
-      <x:c r="E7" s="143"/>
-      <x:c r="F7" s="144" t="str">
-        <x:v>Source record below</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="34" customHeight="1">
-      <x:c r="A8" s="139" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="143" t="str">
-        <x:v>Build DDM, FCFF, and relative valuation formulas with cell links only.</x:v>
-      </x:c>
-      <x:c r="C8" s="143"/>
-      <x:c r="D8" s="143"/>
-      <x:c r="E8" s="143"/>
-      <x:c r="F8" s="144" t="str">
-        <x:v>Valuation comparison</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="139" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B9" s="143" t="str">
-        <x:v>Build each scenario's earnings, sources and uses, balance sheet, ratios, and per-share effects.</x:v>
-      </x:c>
-      <x:c r="C9" s="143"/>
-      <x:c r="D9" s="143"/>
-      <x:c r="E9" s="143"/>
-      <x:c r="F9" s="144" t="str">
-        <x:v>Reconciled scenarios</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="34" customHeight="1">
-      <x:c r="A10" s="139" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="143" t="str">
-        <x:v>Investigate every CHECK; do not interpret a scenario until all required controls pass.</x:v>
-      </x:c>
-      <x:c r="C10" s="143"/>
-      <x:c r="D10" s="143"/>
-      <x:c r="E10" s="143"/>
-      <x:c r="F10" s="144" t="str">
-        <x:v>PASS controls</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="34" customHeight="1">
-      <x:c r="A11" s="140" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B11" s="123" t="str">
-        <x:v>Defend an offer-price and proceeds-deployment recommendation with evidence and a monitoring trigger.</x:v>
-      </x:c>
-      <x:c r="C11" s="123"/>
-      <x:c r="D11" s="123"/>
-      <x:c r="E11" s="123"/>
-      <x:c r="F11" s="124" t="str">
-        <x:v>Decision output</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="23" customHeight="1">
-      <x:c r="A13" s="11" t="str">
-        <x:v>FACTSET EVIDENCE LOG</x:v>
-      </x:c>
-      <x:c r="B13" s="11"/>
-      <x:c r="C13" s="11"/>
-      <x:c r="D13" s="11"/>
-      <x:c r="E13" s="11"/>
-      <x:c r="F13" s="11"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="16" t="str">
-        <x:v>Input</x:v>
-      </x:c>
-      <x:c r="B14" s="16" t="str">
-        <x:v>Field / definition</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="str">
-        <x:v>Company / peer set</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="str">
-        <x:v>Period</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="str">
-        <x:v>Units / currency</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="str">
-        <x:v>Source note / retrieval date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="31" customHeight="1">
-      <x:c r="A15" s="35" t="str">
-        <x:v>Offer / market input</x:v>
-      </x:c>
-      <x:c r="B15" s="86"/>
-      <x:c r="C15" s="86"/>
-      <x:c r="D15" s="86"/>
-      <x:c r="E15" s="86"/>
-      <x:c r="F15" s="86"/>
-    </x:row>
-    <x:row r="16" ht="31" customHeight="1">
-      <x:c r="A16" s="38" t="str">
-        <x:v>Financial statement input</x:v>
-      </x:c>
-      <x:c r="B16" s="86"/>
-      <x:c r="C16" s="86"/>
-      <x:c r="D16" s="86"/>
-      <x:c r="E16" s="86"/>
-      <x:c r="F16" s="86"/>
-    </x:row>
-    <x:row r="17" ht="31" customHeight="1">
-      <x:c r="A17" s="38" t="str">
-        <x:v>Risk / discount-rate input</x:v>
-      </x:c>
-      <x:c r="B17" s="86"/>
-      <x:c r="C17" s="86"/>
-      <x:c r="D17" s="86"/>
-      <x:c r="E17" s="86"/>
-      <x:c r="F17" s="86"/>
-    </x:row>
-    <x:row r="18" ht="31" customHeight="1">
-      <x:c r="A18" s="38" t="str">
-        <x:v>Peer P/E input</x:v>
-      </x:c>
-      <x:c r="B18" s="86"/>
-      <x:c r="C18" s="86"/>
-      <x:c r="D18" s="86"/>
-      <x:c r="E18" s="86"/>
-      <x:c r="F18" s="86"/>
-    </x:row>
-    <x:row r="19" ht="31" customHeight="1">
-      <x:c r="A19" s="41" t="str">
-        <x:v>Peer P/S input</x:v>
-      </x:c>
-      <x:c r="B19" s="86"/>
-      <x:c r="C19" s="86"/>
-      <x:c r="D19" s="86"/>
-      <x:c r="E19" s="86"/>
-      <x:c r="F19" s="86"/>
-    </x:row>
-    <x:row r="21" ht="23" customHeight="1">
-      <x:c r="A21" s="11" t="str">
-        <x:v>SUBMISSION STANDARD</x:v>
-      </x:c>
-      <x:c r="B21" s="11"/>
-      <x:c r="C21" s="11"/>
-      <x:c r="D21" s="11"/>
-      <x:c r="E21" s="11"/>
-      <x:c r="F21" s="11"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="16" t="str">
-        <x:v>Requirement</x:v>
-      </x:c>
-      <x:c r="B22" s="16" t="str">
-        <x:v>Self-check</x:v>
-      </x:c>
-      <x:c r="C22" s="16"/>
-      <x:c r="D22" s="16"/>
-      <x:c r="E22" s="16"/>
-      <x:c r="F22" s="16" t="str">
-        <x:v>Why it matters</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="145" t="str">
-        <x:v>No case numbers typed inside calculation formulas</x:v>
-      </x:c>
-      <x:c r="B23" s="86"/>
-      <x:c r="C23" s="86"/>
-      <x:c r="D23" s="86"/>
-      <x:c r="E23" s="86"/>
-      <x:c r="F23" s="37" t="str">
-        <x:v>Assumptions remain traceable</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="146" t="str">
-        <x:v>All valuation checks are PASS</x:v>
-      </x:c>
-      <x:c r="B24" s="86"/>
-      <x:c r="C24" s="86"/>
-      <x:c r="D24" s="86"/>
-      <x:c r="E24" s="86"/>
-      <x:c r="F24" s="40" t="str">
-        <x:v>Valuation bridges and denominators are valid</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="146" t="str">
-        <x:v>All three sources-and-uses schedules tie</x:v>
-      </x:c>
-      <x:c r="B25" s="86"/>
-      <x:c r="C25" s="86"/>
-      <x:c r="D25" s="86"/>
-      <x:c r="E25" s="86"/>
-      <x:c r="F25" s="40" t="str">
-        <x:v>No proceeds are lost or double counted</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="146" t="str">
-        <x:v>All three post-IPO balance sheets tie</x:v>
-      </x:c>
-      <x:c r="B26" s="86"/>
-      <x:c r="C26" s="86"/>
-      <x:c r="D26" s="86"/>
-      <x:c r="E26" s="86"/>
-      <x:c r="F26" s="40" t="str">
-        <x:v>Cash, debt, assets, and equity reconcile</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="146" t="str">
-        <x:v>Share-count and per-share checks are PASS</x:v>
-      </x:c>
-      <x:c r="B27" s="86"/>
-      <x:c r="C27" s="86"/>
-      <x:c r="D27" s="86"/>
-      <x:c r="E27" s="86"/>
-      <x:c r="F27" s="40" t="str">
-        <x:v>Dilution and ownership effects are consistent</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="146" t="str">
-        <x:v>Every ratio uses the stated numerator and denominator</x:v>
-      </x:c>
-      <x:c r="B28" s="86"/>
-      <x:c r="C28" s="86"/>
-      <x:c r="D28" s="86"/>
-      <x:c r="E28" s="86"/>
-      <x:c r="F28" s="40" t="str">
-        <x:v>Definitions are financially correct</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="32" customHeight="1">
-      <x:c r="A29" s="122" t="str">
-        <x:v>Recommendation cites valuation, deployment, and per-share evidence</x:v>
-      </x:c>
-      <x:c r="B29" s="86"/>
-      <x:c r="C29" s="86"/>
-      <x:c r="D29" s="86"/>
-      <x:c r="E29" s="86"/>
-      <x:c r="F29" s="43" t="str">
-        <x:v>Decision follows from the model</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="163" t="str">
-        <x:v>Important: Apex is fictional. The $164,250 ($000s) net-income value is maintained because it exactly reconciles $219,000 EBT less $54,750 tax. The earlier $164,500 ratio input was an error. Public student materials intentionally omit completed calculation formulas and expected recommendations.</x:v>
-      </x:c>
-      <x:c r="B31" s="164"/>
-      <x:c r="C31" s="164"/>
-      <x:c r="D31" s="164"/>
-      <x:c r="E31" s="164"/>
-      <x:c r="F31" s="165"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="166"/>
-      <x:c r="B32" s="167"/>
-      <x:c r="C32" s="167"/>
-      <x:c r="D32" s="167"/>
-      <x:c r="E32" s="167"/>
-      <x:c r="F32" s="168"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="169"/>
-      <x:c r="B33" s="170"/>
-      <x:c r="C33" s="170"/>
-      <x:c r="D33" s="170"/>
-      <x:c r="E33" s="170"/>
-      <x:c r="F33" s="171"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A4:F4"/>
-    <x:mergeCell ref="B5:E5"/>
-    <x:mergeCell ref="B6:E6"/>
-    <x:mergeCell ref="B7:E7"/>
-    <x:mergeCell ref="B8:E8"/>
-    <x:mergeCell ref="B9:E9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A21:F21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="A31:F33"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>